--- a/iShares/DuurzaamFundamentals.xlsx
+++ b/iShares/DuurzaamFundamentals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerben\Google Drive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\iShares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BEC45C-7322-4C0F-8831-2442E5D97C6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB2BA2E-45B2-4461-AC3E-2547922C9EA5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38535" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
   <si>
     <t>SAWD heeft zo'n 100 uitsluitingen. Lijkt wat op NT world.</t>
   </si>
@@ -146,13 +146,16 @@
   </si>
   <si>
     <t>fundcomp</t>
+  </si>
+  <si>
+    <t>ESG screen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +187,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -202,21 +212,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Procent" xfId="2" builtinId="5"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -971,6 +985,9 @@
       <c r="C2" s="1">
         <v>44104</v>
       </c>
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -980,6 +997,14 @@
       <c r="C3">
         <v>21.68</v>
       </c>
+      <c r="E3" s="6">
+        <f>1/C3</f>
+        <v>4.6125461254612546E-2</v>
+      </c>
+      <c r="G3" s="7">
+        <f>E3-E8</f>
+        <v>1.302511904545306E-3</v>
+      </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -988,21 +1013,44 @@
       <c r="C4">
         <v>21.83</v>
       </c>
+      <c r="E4" s="6">
+        <f t="shared" ref="E4:E12" si="0">1/C4</f>
+        <v>4.5808520384791572E-2</v>
+      </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="C5">
+        <v>21.69</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="0"/>
+        <v>4.6104195481788839E-2</v>
+      </c>
+      <c r="G5" s="7">
+        <f>E5-E7</f>
+        <v>9.3707714393879288E-4</v>
+      </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="C7">
+        <v>22.14</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>4.5167118337850046E-2</v>
+      </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
@@ -1011,11 +1059,22 @@
       <c r="C8">
         <v>22.31</v>
       </c>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>4.482294935006724E-2</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="C9">
+        <v>21.72</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>4.6040515653775323E-2</v>
+      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
@@ -1024,11 +1083,16 @@
       <c r="C10">
         <v>21.68</v>
       </c>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>4.6125461254612546E-2</v>
+      </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -1037,21 +1101,29 @@
       <c r="C12">
         <v>23.18</v>
       </c>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>4.3140638481449528E-2</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C17">
         <v>2.2599999999999998</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <f>C17-C22</f>
+        <v>-6.0000000000000053E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>32</v>
       </c>
@@ -1059,22 +1131,32 @@
         <v>2.2200000000000002</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="G19">
+        <f>C19-C21</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
@@ -1082,12 +1164,15 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>2.2599999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>13</v>
       </c>
@@ -1095,12 +1180,12 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="4" t="s">
         <v>14</v>
       </c>
@@ -1108,7 +1193,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>34</v>
       </c>
@@ -1116,7 +1201,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
         <v>9</v>
       </c>
@@ -1127,7 +1212,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
@@ -1135,7 +1220,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
         <v>33</v>
       </c>
@@ -1205,6 +1290,18 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E3:E12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{78E1AFD6-9F96-40B9-BDF6-7B21AAC8AA5B}"/>
     <hyperlink ref="B6" r:id="rId2" xr:uid="{16D5CAA8-E0EE-4989-9627-22BEE6F3FC3D}"/>
